--- a/data.xlsx
+++ b/data.xlsx
@@ -1205,11 +1205,31 @@
         </is>
       </c>
       <c r="K6" s="9" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>audio/ru_p1.m4a</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>audio/ru_p2.m4a</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>audio/ru_p3.m4a</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>audio/ru_p4.m4a</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>audio/ru_p5.m4a</t>
+        </is>
+      </c>
       <c r="Q6" s="7" t="n"/>
       <c r="R6" s="7" t="n"/>
     </row>
@@ -1289,11 +1309,31 @@
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p1.mp3</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p2.mp3</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p3.mp3</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p4.mp3</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p5.mp3</t>
+        </is>
+      </c>
       <c r="Q8" s="7" t="n"/>
       <c r="R8" s="7" t="n"/>
     </row>
@@ -1329,11 +1369,31 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p1.mp3</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p2.mp3</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p3.mp3</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p4.mp3</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>audio/ar_p5.mp3</t>
+        </is>
+      </c>
       <c r="Q9" s="7" t="n"/>
       <c r="R9" s="7" t="n"/>
     </row>
@@ -1369,11 +1429,31 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>audio/ps_p1.mp3</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>audio/ps_p2.mp3</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>audio/ps_p3.mp3</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>audio/ps_p4.mp3</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>audio/ps_p5.mp3</t>
+        </is>
+      </c>
       <c r="Q10" s="7" t="n"/>
       <c r="R10" s="7" t="n"/>
     </row>
@@ -1657,11 +1737,31 @@
         </is>
       </c>
       <c r="K17" s="9" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>audio/hy_p1.m4a</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>audio/hy_p2.m4a</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>audio/hy_p3.m4a</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>audio/hy_p4.m4a</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>audio/hy_p5.m4a</t>
+        </is>
+      </c>
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="7" t="n"/>
     </row>
@@ -2181,11 +2281,31 @@
         </is>
       </c>
       <c r="K29" s="9" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>audio/ff_p1.mp3</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>audio/ff_p2.mp3</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>audio/ff_p3.mp3</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>audio/ff_p4.mp3</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>audio/ff_p5.mp3</t>
+        </is>
+      </c>
       <c r="Q29" s="7" t="n"/>
       <c r="R29" s="7" t="n"/>
     </row>
